--- a/questionnaire_templates/047_public_policy_initiative_feedback_questionnaire--questionnaire_templates.xlsx
+++ b/questionnaire_templates/047_public_policy_initiative_feedback_questionnaire--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,10 +525,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>user_info</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>1. User Information</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please provide your name and email address</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -543,18 +547,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>feedback_rating</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>feedback_rating</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>2. Feedback Rating (1-5)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Rate your feedback on the policy initiative</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,18 +574,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>comment</t>
+          <t>feedback_comment</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>feedback_comment</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>3. Feedback Comment</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please provide a brief comment on the policy initiative</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,13 +606,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>policy_areas</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>4. Policy Areas of Interest</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Select all areas that apply</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,18 +628,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>feedback_email</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>feedback_email</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>5. Feedback Email</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Provide your email address for feedback</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,18 +655,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>feedback_phone</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>feedback_phone</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>6. Feedback Phone</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Provide your phone number for feedback</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -663,13 +687,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>submission_date</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>7. Submission Date</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Select the submission date</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -686,13 +714,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>submission_time</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>8. Submission Time</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Select the submission time</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -709,13 +741,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>submission_date_time</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>9. Submission Date and Time</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Select the submission date and time</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -732,33 +768,41 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>10. Submit</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please submit your feedback</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>policy_area_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>feedback_email</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>11. Policy Area 1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Select the policy area</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -768,159 +812,25 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>policy_area_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>feedback_phone</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>12. Policy Area 2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Select the policy area</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>submission_date</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>submission_date</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>submission_time</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>submission_time</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>submission_date_time</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>submission_date_time</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>policy_area_1</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>policy_area_1</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>policy_area_2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>policy_area_2</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -937,12 +847,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -970,12 +880,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>policy_area_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>Policy Area 1</t>
         </is>
       </c>
     </row>
@@ -987,12 +897,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>policy_area_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>Policy Area 2</t>
         </is>
       </c>
     </row>
@@ -1004,12 +914,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>policy_area_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>Policy Area 3</t>
         </is>
       </c>
     </row>
@@ -1021,12 +931,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>policy_area_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>Policy Area 4</t>
         </is>
       </c>
     </row>
@@ -1038,12 +948,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_5</t>
+          <t>policy_area_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option_5</t>
+          <t>Policy Area 5</t>
         </is>
       </c>
     </row>
@@ -1055,12 +965,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>policy_area_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>Policy Area 1</t>
         </is>
       </c>
     </row>
@@ -1072,12 +982,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>policy_area_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>Policy Area 2</t>
         </is>
       </c>
     </row>
@@ -1089,12 +999,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>policy_area_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>Policy Area 3</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1016,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>policy_area_4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>Policy Area 4</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1033,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option_5</t>
+          <t>policy_area_5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option_5</t>
+          <t>Policy Area 5</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1050,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>policy_area_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Policy Area 1</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1067,63 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>policy_area_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Policy Area 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>policy_area_2_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>policy_area_3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Policy Area 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>policy_area_2_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>policy_area_4</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Policy Area 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>policy_area_2_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>policy_area_5</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Policy Area 5</t>
         </is>
       </c>
     </row>
